--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -931,6 +931,116 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>114932698</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57236</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Tenngårdsholmen, Hammarön, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>418237</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6575128</v>
+      </c>
+      <c r="S4" t="n">
+        <v>75</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-04-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-04-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Åke Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Åke Johansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1284,6 +1284,480 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120384522</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tenngårdsholmen, Tenngårdsholmen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>418231</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6575132</v>
+      </c>
+      <c r="S7" t="n">
+        <v>4</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Nim Rautiainen Byström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Nim Rautiainen Byström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120382940</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tenngårdsholmen, Tenngårdsholmen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>418252</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6575130</v>
+      </c>
+      <c r="S8" t="n">
+        <v>9</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120384826</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tenngårdsholmen, Tenngårdsholmen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>418265</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6575147</v>
+      </c>
+      <c r="S9" t="n">
+        <v>7</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Pia Edfors</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120383082</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tenngårdsholmen, Tenngårdsholmen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>418250</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6575066</v>
+      </c>
+      <c r="S10" t="n">
+        <v>6</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:51</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Nim Rautiainen Byström</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Nim Rautiainen Byström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -1286,7 +1286,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120384522</v>
+        <v>120382940</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1321,7 +1321,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1330,13 +1335,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>418231</v>
+        <v>418252</v>
       </c>
       <c r="R7" t="n">
-        <v>6575132</v>
+        <v>6575130</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1365,7 +1370,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1375,7 +1380,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1390,19 +1395,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Nim Rautiainen Byström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Nim Rautiainen Byström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120382940</v>
+        <v>120384826</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1437,12 +1442,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1451,13 +1456,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>418252</v>
+        <v>418265</v>
       </c>
       <c r="R8" t="n">
-        <v>6575130</v>
+        <v>6575147</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1486,7 +1491,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1496,7 +1501,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1523,7 +1528,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120384826</v>
+        <v>120384522</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1558,12 +1563,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>418265</v>
+        <v>418231</v>
       </c>
       <c r="R9" t="n">
-        <v>6575147</v>
+        <v>6575132</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1632,12 +1632,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Nim Rautiainen Byström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Nim Rautiainen Byström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -1286,7 +1286,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120382940</v>
+        <v>120384522</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1321,12 +1321,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1335,13 +1330,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>418252</v>
+        <v>418231</v>
       </c>
       <c r="R7" t="n">
-        <v>6575130</v>
+        <v>6575132</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1370,7 +1365,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1380,7 +1375,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,12 +1390,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Nim Rautiainen Byström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Nim Rautiainen Byström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1528,7 +1523,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120384522</v>
+        <v>120383082</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1563,7 +1558,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>32</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1572,13 +1567,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>418231</v>
+        <v>418250</v>
       </c>
       <c r="R9" t="n">
-        <v>6575132</v>
+        <v>6575066</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1607,7 +1602,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1617,7 +1612,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1644,7 +1639,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120383082</v>
+        <v>120382940</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1679,7 +1674,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1688,13 +1688,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>418250</v>
+        <v>418252</v>
       </c>
       <c r="R10" t="n">
-        <v>6575066</v>
+        <v>6575130</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1748,12 +1748,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Nim Rautiainen Byström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Nim Rautiainen Byström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -1286,7 +1286,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120384522</v>
+        <v>120383082</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>32</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1330,13 +1330,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>418231</v>
+        <v>418250</v>
       </c>
       <c r="R7" t="n">
-        <v>6575132</v>
+        <v>6575066</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1402,7 +1402,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120384826</v>
+        <v>120384522</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1437,12 +1437,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1451,13 +1446,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>418265</v>
+        <v>418231</v>
       </c>
       <c r="R8" t="n">
-        <v>6575147</v>
+        <v>6575132</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1486,7 +1481,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1496,7 +1491,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,19 +1506,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Nim Rautiainen Byström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Nim Rautiainen Byström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120383082</v>
+        <v>120382940</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1558,7 +1553,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1567,13 +1567,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>418250</v>
+        <v>418252</v>
       </c>
       <c r="R9" t="n">
-        <v>6575066</v>
+        <v>6575130</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1627,19 +1627,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Nim Rautiainen Byström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Nim Rautiainen Byström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120382940</v>
+        <v>120384826</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1674,12 +1674,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1688,13 +1688,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>418252</v>
+        <v>418265</v>
       </c>
       <c r="R10" t="n">
-        <v>6575130</v>
+        <v>6575147</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -1402,7 +1402,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120384522</v>
+        <v>120382940</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1437,7 +1437,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1446,13 +1451,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>418231</v>
+        <v>418252</v>
       </c>
       <c r="R8" t="n">
-        <v>6575132</v>
+        <v>6575130</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1481,7 +1486,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1491,7 +1496,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1506,19 +1511,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Nim Rautiainen Byström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Nim Rautiainen Byström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120382940</v>
+        <v>120384522</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1553,12 +1558,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1567,13 +1567,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>418252</v>
+        <v>418231</v>
       </c>
       <c r="R9" t="n">
-        <v>6575130</v>
+        <v>6575132</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1627,12 +1627,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Nim Rautiainen Byström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Nim Rautiainen Byström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -1286,7 +1286,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120383082</v>
+        <v>120382940</v>
       </c>
       <c r="B7" t="n">
         <v>97930</v>
@@ -1321,7 +1321,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1330,13 +1335,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>418250</v>
+        <v>418252</v>
       </c>
       <c r="R7" t="n">
-        <v>6575066</v>
+        <v>6575130</v>
       </c>
       <c r="S7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1365,7 +1370,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1375,7 +1380,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:51</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1390,19 +1395,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Nim Rautiainen Byström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Nim Rautiainen Byström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120382940</v>
+        <v>120384522</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1437,12 +1442,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1451,13 +1451,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>418252</v>
+        <v>418231</v>
       </c>
       <c r="R8" t="n">
-        <v>6575130</v>
+        <v>6575132</v>
       </c>
       <c r="S8" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,19 +1511,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Nim Rautiainen Byström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Nim Rautiainen Byström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120384522</v>
+        <v>120383082</v>
       </c>
       <c r="B9" t="n">
         <v>97930</v>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>32</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1567,13 +1567,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>418231</v>
+        <v>418250</v>
       </c>
       <c r="R9" t="n">
-        <v>6575132</v>
+        <v>6575066</v>
       </c>
       <c r="S9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:51</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -1407,7 +1407,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120384522</v>
+        <v>120384826</v>
       </c>
       <c r="B8" t="n">
         <v>97930</v>
@@ -1442,7 +1442,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1451,13 +1456,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>418231</v>
+        <v>418265</v>
       </c>
       <c r="R8" t="n">
-        <v>6575132</v>
+        <v>6575147</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1486,7 +1491,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1496,7 +1501,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,12 +1516,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Nim Rautiainen Byström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Nim Rautiainen Byström</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1639,7 +1644,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120384826</v>
+        <v>120384522</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1674,12 +1679,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1688,13 +1688,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>418265</v>
+        <v>418231</v>
       </c>
       <c r="R10" t="n">
-        <v>6575147</v>
+        <v>6575132</v>
       </c>
       <c r="S10" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1723,7 +1723,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1748,12 +1748,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Nim Rautiainen Byström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Nim Rautiainen Byström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -1760,7 +1760,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124300104</v>
+        <v>124299908</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>418321</v>
+        <v>418255</v>
       </c>
       <c r="R11" t="n">
-        <v>6575049</v>
+        <v>6575112</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1881,7 +1881,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124299695</v>
+        <v>124300104</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>418228</v>
+        <v>418321</v>
       </c>
       <c r="R12" t="n">
-        <v>6575105</v>
+        <v>6575049</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2002,10 +2002,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124299799</v>
+        <v>124299695</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2014,35 +2014,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>418229</v>
+        <v>418228</v>
       </c>
       <c r="R13" t="n">
-        <v>6575106</v>
+        <v>6575105</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2123,10 +2123,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124299908</v>
+        <v>124299799</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2135,35 +2135,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>418255</v>
+        <v>418229</v>
       </c>
       <c r="R14" t="n">
-        <v>6575112</v>
+        <v>6575106</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -1760,10 +1760,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124299908</v>
+        <v>124299799</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1772,35 +1772,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>418255</v>
+        <v>418229</v>
       </c>
       <c r="R11" t="n">
-        <v>6575112</v>
+        <v>6575106</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2123,10 +2123,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124299799</v>
+        <v>124299908</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2135,35 +2135,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>418229</v>
+        <v>418255</v>
       </c>
       <c r="R14" t="n">
-        <v>6575106</v>
+        <v>6575112</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -1881,7 +1881,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124300104</v>
+        <v>124299695</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>418321</v>
+        <v>418228</v>
       </c>
       <c r="R12" t="n">
-        <v>6575049</v>
+        <v>6575105</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2002,7 +2002,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124299695</v>
+        <v>124300104</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>418228</v>
+        <v>418321</v>
       </c>
       <c r="R13" t="n">
-        <v>6575105</v>
+        <v>6575049</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -1760,10 +1760,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124299799</v>
+        <v>124299695</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1772,35 +1772,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>418229</v>
+        <v>418228</v>
       </c>
       <c r="R11" t="n">
-        <v>6575106</v>
+        <v>6575105</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1881,10 +1881,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124299695</v>
+        <v>124299799</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1893,35 +1893,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>418228</v>
+        <v>418229</v>
       </c>
       <c r="R12" t="n">
-        <v>6575105</v>
+        <v>6575106</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD12" t="b">

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -1760,10 +1760,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124299695</v>
+        <v>124299799</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1772,35 +1772,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>418228</v>
+        <v>418229</v>
       </c>
       <c r="R11" t="n">
-        <v>6575105</v>
+        <v>6575106</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1881,10 +1881,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124299799</v>
+        <v>124299908</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1893,35 +1893,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>418229</v>
+        <v>418255</v>
       </c>
       <c r="R12" t="n">
-        <v>6575106</v>
+        <v>6575112</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2002,7 +2002,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124300104</v>
+        <v>124299695</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>418321</v>
+        <v>418228</v>
       </c>
       <c r="R13" t="n">
-        <v>6575049</v>
+        <v>6575105</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2123,7 +2123,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124299908</v>
+        <v>124300104</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>418255</v>
+        <v>418321</v>
       </c>
       <c r="R14" t="n">
-        <v>6575112</v>
+        <v>6575049</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -1760,10 +1760,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124299799</v>
+        <v>124299695</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1772,35 +1772,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>418229</v>
+        <v>418228</v>
       </c>
       <c r="R11" t="n">
-        <v>6575106</v>
+        <v>6575105</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2002,7 +2002,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124299695</v>
+        <v>124300104</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>418228</v>
+        <v>418321</v>
       </c>
       <c r="R13" t="n">
-        <v>6575105</v>
+        <v>6575049</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2123,10 +2123,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124300104</v>
+        <v>124299799</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2135,35 +2135,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>418321</v>
+        <v>418229</v>
       </c>
       <c r="R14" t="n">
-        <v>6575049</v>
+        <v>6575106</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -1760,7 +1760,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124299695</v>
+        <v>124300104</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>418228</v>
+        <v>418321</v>
       </c>
       <c r="R11" t="n">
-        <v>6575105</v>
+        <v>6575049</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2002,10 +2002,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124300104</v>
+        <v>124299799</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2014,35 +2014,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>418321</v>
+        <v>418229</v>
       </c>
       <c r="R13" t="n">
-        <v>6575049</v>
+        <v>6575106</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2123,10 +2123,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124299799</v>
+        <v>124299695</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2135,35 +2135,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>418229</v>
+        <v>418228</v>
       </c>
       <c r="R14" t="n">
-        <v>6575106</v>
+        <v>6575105</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -1760,7 +1760,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124300104</v>
+        <v>124299695</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>418321</v>
+        <v>418228</v>
       </c>
       <c r="R11" t="n">
-        <v>6575049</v>
+        <v>6575105</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2002,10 +2002,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124299799</v>
+        <v>124300104</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2014,35 +2014,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>418229</v>
+        <v>418321</v>
       </c>
       <c r="R13" t="n">
-        <v>6575106</v>
+        <v>6575049</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2123,10 +2123,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124299695</v>
+        <v>124299799</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2135,35 +2135,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>418228</v>
+        <v>418229</v>
       </c>
       <c r="R14" t="n">
-        <v>6575105</v>
+        <v>6575106</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -1760,10 +1760,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124299695</v>
+        <v>124299799</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1772,35 +1772,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>418228</v>
+        <v>418229</v>
       </c>
       <c r="R11" t="n">
-        <v>6575105</v>
+        <v>6575106</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1881,7 +1881,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124299908</v>
+        <v>124299695</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -1916,7 +1916,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>418255</v>
+        <v>418228</v>
       </c>
       <c r="R12" t="n">
-        <v>6575112</v>
+        <v>6575105</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2123,10 +2123,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124299799</v>
+        <v>124299908</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2135,35 +2135,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>418229</v>
+        <v>418255</v>
       </c>
       <c r="R14" t="n">
-        <v>6575106</v>
+        <v>6575112</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -1760,10 +1760,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124299799</v>
+        <v>124299695</v>
       </c>
       <c r="B11" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1772,35 +1772,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>418229</v>
+        <v>418228</v>
       </c>
       <c r="R11" t="n">
-        <v>6575106</v>
+        <v>6575105</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1881,10 +1881,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124299695</v>
+        <v>124299799</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1893,35 +1893,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>418228</v>
+        <v>418229</v>
       </c>
       <c r="R12" t="n">
-        <v>6575105</v>
+        <v>6575106</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2002,7 +2002,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124300104</v>
+        <v>124299908</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>418321</v>
+        <v>418255</v>
       </c>
       <c r="R13" t="n">
-        <v>6575049</v>
+        <v>6575112</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2123,7 +2123,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124299908</v>
+        <v>124300104</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>418255</v>
+        <v>418321</v>
       </c>
       <c r="R14" t="n">
-        <v>6575112</v>
+        <v>6575049</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -1760,7 +1760,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124299695</v>
+        <v>124299908</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>418228</v>
+        <v>418255</v>
       </c>
       <c r="R11" t="n">
-        <v>6575105</v>
+        <v>6575112</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1881,10 +1881,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124299799</v>
+        <v>124300104</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1893,35 +1893,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>418229</v>
+        <v>418321</v>
       </c>
       <c r="R12" t="n">
-        <v>6575106</v>
+        <v>6575049</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2002,7 +2002,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124299908</v>
+        <v>124299695</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>418255</v>
+        <v>418228</v>
       </c>
       <c r="R13" t="n">
-        <v>6575112</v>
+        <v>6575105</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2123,10 +2123,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124300104</v>
+        <v>124299799</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2135,35 +2135,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2172,10 +2172,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>418321</v>
+        <v>418229</v>
       </c>
       <c r="R14" t="n">
-        <v>6575049</v>
+        <v>6575106</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2242,6 +2242,132 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128919685</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98632</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Tenngårdsholmen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>418286</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6575135</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ca 20-30 plantor inom 3m2.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Alice Högström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Alice Högström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2247,7 +2247,7 @@
         <v>128919685</v>
       </c>
       <c r="B15" t="n">
-        <v>98632</v>
+        <v>98636</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2247,7 +2247,7 @@
         <v>128919685</v>
       </c>
       <c r="B15" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2247,7 +2247,7 @@
         <v>128919685</v>
       </c>
       <c r="B15" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2247,7 +2247,7 @@
         <v>128919685</v>
       </c>
       <c r="B15" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2247,7 +2247,7 @@
         <v>128919685</v>
       </c>
       <c r="B15" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2247,7 +2247,7 @@
         <v>128919685</v>
       </c>
       <c r="B15" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2247,7 +2247,7 @@
         <v>128919685</v>
       </c>
       <c r="B15" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2247,7 +2247,7 @@
         <v>128919685</v>
       </c>
       <c r="B15" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2247,7 +2247,7 @@
         <v>128919685</v>
       </c>
       <c r="B15" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2367,6 +2367,126 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>124299992</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98705</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Tenngårdsholmen, Tenngårdsholmen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>418282</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6575062</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2247,7 +2247,7 @@
         <v>128919685</v>
       </c>
       <c r="B15" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>124299992</v>
       </c>
       <c r="B16" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2247,7 +2247,7 @@
         <v>128919685</v>
       </c>
       <c r="B15" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>124299992</v>
       </c>
       <c r="B16" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2247,7 +2247,7 @@
         <v>128919685</v>
       </c>
       <c r="B15" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>124299992</v>
       </c>
       <c r="B16" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2247,7 +2247,7 @@
         <v>128919685</v>
       </c>
       <c r="B15" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>124299992</v>
       </c>
       <c r="B16" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2373,7 +2373,7 @@
         <v>124299992</v>
       </c>
       <c r="B16" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2373,7 +2373,7 @@
         <v>124299992</v>
       </c>
       <c r="B16" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2373,7 +2373,7 @@
         <v>124299992</v>
       </c>
       <c r="B16" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2373,7 +2373,7 @@
         <v>124299992</v>
       </c>
       <c r="B16" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2373,7 +2373,7 @@
         <v>124299992</v>
       </c>
       <c r="B16" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2373,7 +2373,7 @@
         <v>124299992</v>
       </c>
       <c r="B16" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2373,7 +2373,7 @@
         <v>124299992</v>
       </c>
       <c r="B16" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2373,7 +2373,7 @@
         <v>124299992</v>
       </c>
       <c r="B16" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2488,6 +2488,364 @@
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129922698</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98790</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Tenngårdsholmen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>418322</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6575049</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>S-Ham-0056</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129922697</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98790</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Tenngårdsholmen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>418282</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6575061</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>S-Ham-0057</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129922695</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98790</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Tenngårdsholmen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>418287</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6575135</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>S-Ham-0059</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ca 20-30 plantor inom 3m2.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Alice Högström</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2493,7 +2493,7 @@
         <v>129922698</v>
       </c>
       <c r="B17" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>129922697</v>
       </c>
       <c r="B18" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>129922695</v>
       </c>
       <c r="B19" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2493,7 +2493,7 @@
         <v>129922698</v>
       </c>
       <c r="B17" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>129922697</v>
       </c>
       <c r="B18" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>129922695</v>
       </c>
       <c r="B19" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2493,7 +2493,7 @@
         <v>129922698</v>
       </c>
       <c r="B17" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>129922697</v>
       </c>
       <c r="B18" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>129922695</v>
       </c>
       <c r="B19" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2493,7 +2493,7 @@
         <v>129922698</v>
       </c>
       <c r="B17" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>129922697</v>
       </c>
       <c r="B18" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>129922695</v>
       </c>
       <c r="B19" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2493,7 +2493,7 @@
         <v>129922698</v>
       </c>
       <c r="B17" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>129922697</v>
       </c>
       <c r="B18" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>129922695</v>
       </c>
       <c r="B19" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2493,7 +2493,7 @@
         <v>129922698</v>
       </c>
       <c r="B17" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>129922697</v>
       </c>
       <c r="B18" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         <v>129922695</v>
       </c>
       <c r="B19" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2851,7 +2851,7 @@
         <v>132329253</v>
       </c>
       <c r="B20" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>132329250</v>
       </c>
       <c r="B21" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2851,7 +2851,7 @@
         <v>132329253</v>
       </c>
       <c r="B20" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>132329250</v>
       </c>
       <c r="B21" t="n">
-        <v>99098</v>
+        <v>99106</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2851,7 +2851,7 @@
         <v>132329253</v>
       </c>
       <c r="B20" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>132329250</v>
       </c>
       <c r="B21" t="n">
-        <v>99106</v>
+        <v>99116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2851,7 +2851,7 @@
         <v>132329253</v>
       </c>
       <c r="B20" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>132329250</v>
       </c>
       <c r="B21" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2851,7 +2851,7 @@
         <v>132329253</v>
       </c>
       <c r="B20" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>132329250</v>
       </c>
       <c r="B21" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2851,7 +2851,7 @@
         <v>132329253</v>
       </c>
       <c r="B20" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>132329250</v>
       </c>
       <c r="B21" t="n">
-        <v>99118</v>
+        <v>99119</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2851,7 +2851,7 @@
         <v>132329253</v>
       </c>
       <c r="B20" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>132329250</v>
       </c>
       <c r="B21" t="n">
-        <v>99119</v>
+        <v>99121</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2851,7 +2851,7 @@
         <v>132329253</v>
       </c>
       <c r="B20" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>132329250</v>
       </c>
       <c r="B21" t="n">
-        <v>99121</v>
+        <v>99122</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -2851,7 +2851,7 @@
         <v>132329253</v>
       </c>
       <c r="B20" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>132329250</v>
       </c>
       <c r="B21" t="n">
-        <v>99122</v>
+        <v>99125</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,67 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3044693</v>
+        <v>103401645</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tenngårdsholmen, Vrm</t>
+          <t>Tenngårdsholmen, Hammarön, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>418255.0577623895</v>
+        <v>418237</v>
       </c>
       <c r="R2" t="n">
-        <v>6575179.871727922</v>
+        <v>6575128</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,29 +750,24 @@
           <t>Hammarö</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>S-Ham-0030</t>
-        </is>
-      </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-07-26</t>
+          <t>2022-09-06</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-07-26</t>
+          <t>2022-09-06</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,35 +782,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Värmland Floraväktarna</t>
+          <t>Åke Johansson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erik Eriksson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Åke Johansson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>103401645</v>
+        <v>108216914</v>
       </c>
       <c r="B3" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -852,23 +831,23 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tenngårdsholmen, Hammarön, Vrm</t>
+          <t>Tenngårdsholmern, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>418237.0474849499</v>
+        <v>418204</v>
       </c>
       <c r="R3" t="n">
-        <v>6575127.651613941</v>
+        <v>6574969</v>
       </c>
       <c r="S3" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,22 +871,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-09-06</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-09-06</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I nyckelbiotop söder om kanalen Sättersviken - Torsängsviken</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -918,6 +902,11 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Limnisk strandvåtmark</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -934,32 +923,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>114932698</v>
+        <v>124299799</v>
       </c>
       <c r="B4" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -967,28 +951,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tenngårdsholmen, Hammarön, Vrm</t>
+          <t>Tenngårdsholmen, Tenngårdsholmen, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>418237</v>
+        <v>418229</v>
       </c>
       <c r="R4" t="n">
-        <v>6575128</v>
+        <v>6575106</v>
       </c>
       <c r="S4" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,12 +997,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-04-17</t>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,74 +1027,68 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Åke Johansson</t>
+          <t>Åsa Duell</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Åke Johansson</t>
+          <t>Åsa Duell</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115326284</v>
+        <v>114932698</v>
       </c>
       <c r="B5" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tenngårdsholmen (Tenngårdsholmen), Vrm</t>
+          <t>Tenngårdsholmen, Hammarön, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>418349</v>
+        <v>418237</v>
       </c>
       <c r="R5" t="n">
-        <v>6575081</v>
+        <v>6575128</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,22 +1112,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>17:08</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>17:08</t>
+          <t>2023-04-17</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,27 +1132,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Åsa Duell</t>
+          <t>Åke Johansson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Åsa Duell</t>
+          <t>Åke Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115326450</v>
+        <v>3044693</v>
       </c>
       <c r="B6" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1200,24 +1174,29 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>159</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Tenngårdsholmen (Tenngårdsholmen), Vrm</t>
+          <t>Tenngårdsholmen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>418257</v>
+        <v>418255</v>
       </c>
       <c r="R6" t="n">
-        <v>6575088</v>
+        <v>6575180</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,24 +1221,19 @@
           <t>Hammarö</t>
         </is>
       </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>S-Ham-0030</t>
+        </is>
+      </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>17:18</t>
+          <t>2011-07-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>17:18</t>
+          <t>2011-07-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,27 +1248,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Åsa Duell</t>
+          <t>Värmland Floraväktarna</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Åsa Duell</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Erik Eriksson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120382940</v>
+        <v>115326284</v>
       </c>
       <c r="B7" t="n">
-        <v>98007</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1321,7 +1294,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1335,13 +1308,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>418252</v>
+        <v>418349</v>
       </c>
       <c r="R7" t="n">
-        <v>6575130</v>
+        <v>6575081</v>
       </c>
       <c r="S7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1365,22 +1338,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,27 +1368,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Åsa Duell</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Pia Edfors</t>
+          <t>Åsa Duell</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120384522</v>
+        <v>115326450</v>
       </c>
       <c r="B8" t="n">
-        <v>98007</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1442,7 +1410,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1451,13 +1424,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>418231</v>
+        <v>418257</v>
       </c>
       <c r="R8" t="n">
-        <v>6575132</v>
+        <v>6575088</v>
       </c>
       <c r="S8" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1481,22 +1454,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-13</t>
+          <t>2024-03-22</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,27 +1484,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Nim Rautiainen Byström</t>
+          <t>Åsa Duell</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Nim Rautiainen Byström</t>
+          <t>Åsa Duell</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120384826</v>
+        <v>120382940</v>
       </c>
       <c r="B9" t="n">
-        <v>98007</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,12 +1526,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1572,13 +1540,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>418265</v>
+        <v>418252</v>
       </c>
       <c r="R9" t="n">
-        <v>6575147</v>
+        <v>6575130</v>
       </c>
       <c r="S9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1607,7 +1575,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1617,7 +1585,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1647,12 +1615,7 @@
         <v>120383082</v>
       </c>
       <c r="B10" t="n">
-        <v>98007</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1760,15 +1723,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124299908</v>
+        <v>120384522</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1795,12 +1753,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1809,13 +1762,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>418255</v>
+        <v>418231</v>
       </c>
       <c r="R11" t="n">
-        <v>6575112</v>
+        <v>6575132</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1839,22 +1792,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1869,27 +1822,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Åsa Duell</t>
+          <t>Nim Rautiainen Byström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Åsa Duell</t>
+          <t>Nim Rautiainen Byström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124300104</v>
+        <v>120384826</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1916,12 +1864,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1930,13 +1878,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>418321</v>
+        <v>418265</v>
       </c>
       <c r="R12" t="n">
-        <v>6575049</v>
+        <v>6575147</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1960,22 +1908,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2024-10-13</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1990,12 +1938,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Åsa Duell</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Åsa Duell</t>
+          <t>Pia Edfors</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2005,12 +1953,7 @@
         <v>124299695</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2123,47 +2066,42 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124299799</v>
+        <v>124299908</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2172,10 +2110,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>418229</v>
+        <v>418255</v>
       </c>
       <c r="R14" t="n">
-        <v>6575106</v>
+        <v>6575112</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2207,7 +2145,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2217,7 +2155,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:55</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2244,10 +2182,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128919685</v>
+        <v>124299992</v>
       </c>
       <c r="B15" t="n">
-        <v>98716</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2274,7 +2212,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2282,24 +2220,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Tenngårdsholmen, Vrm</t>
+          <t>Tenngårdsholmen, Tenngårdsholmen, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>418286</v>
+        <v>418282</v>
       </c>
       <c r="R15" t="n">
-        <v>6575135</v>
+        <v>6575062</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2323,27 +2259,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:47</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:47</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ca 20-30 plantor inom 3m2.</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2352,28 +2283,29 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Alice Högström</t>
+          <t>Åsa Duell</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Alice Högström</t>
+          <t>Åsa Duell</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124299992</v>
+        <v>124300104</v>
       </c>
       <c r="B16" t="n">
-        <v>98780</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2400,7 +2332,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2408,19 +2340,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Tenngårdsholmen, Tenngårdsholmen, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>418282</v>
+        <v>418321</v>
       </c>
       <c r="R16" t="n">
-        <v>6575062</v>
+        <v>6575049</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2452,7 +2381,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2462,7 +2391,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2471,7 +2400,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2490,10 +2418,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129922698</v>
+        <v>128919685</v>
       </c>
       <c r="B17" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2520,12 +2448,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2534,13 +2467,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>418322</v>
+        <v>418286</v>
       </c>
       <c r="R17" t="n">
-        <v>6575049</v>
+        <v>6575135</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2562,19 +2495,29 @@
           <t>Hammarö</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>S-Ham-0056</t>
-        </is>
-      </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:47</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ca 20-30 plantor inom 3m2.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2589,26 +2532,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Owe Nilsson</t>
+          <t>Alice Högström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Åsa Duell</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+          <t>Alice Högström</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129922697</v>
+        <v>129922695</v>
       </c>
       <c r="B18" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2635,7 +2574,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2643,16 +2582,23 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Tenngårdsholmen, Vrm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>418282</v>
+        <v>418287</v>
       </c>
       <c r="R18" t="n">
-        <v>6575061</v>
+        <v>6575135</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2679,17 +2625,22 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>S-Ham-0057</t>
+          <t>S-Ham-0059</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-10-05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2025-10-05</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ca 20-30 plantor inom 3m2.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2698,6 +2649,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2709,7 +2661,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Åsa Duell</t>
+          <t>Alice Högström</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
@@ -2720,10 +2672,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129922695</v>
+        <v>129922697</v>
       </c>
       <c r="B19" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2750,7 +2702,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2758,23 +2710,16 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Tenngårdsholmen, Vrm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>418287</v>
+        <v>418282</v>
       </c>
       <c r="R19" t="n">
-        <v>6575135</v>
+        <v>6575061</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2801,22 +2746,17 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>S-Ham-0059</t>
+          <t>S-Ham-0057</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-05</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ca 20-30 plantor inom 3m2.</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2825,7 +2765,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2837,7 +2776,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Alice Högström</t>
+          <t>Åsa Duell</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2848,10 +2787,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132329253</v>
+        <v>129922698</v>
       </c>
       <c r="B20" t="n">
-        <v>99125</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2878,34 +2817,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sundsvik, Sundsvik, Vrm</t>
+          <t>Tenngårdsholmen, Vrm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>418229</v>
+        <v>418322</v>
       </c>
       <c r="R20" t="n">
-        <v>6575106</v>
+        <v>6575049</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2927,24 +2859,19 @@
           <t>Hammarö</t>
         </is>
       </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>S-Ham-0056</t>
+        </is>
+      </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>16:32</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>16:32</t>
+          <t>2025-04-21</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2959,22 +2886,26 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
+          <t>Owe Nilsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
           <t>Åsa Duell</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Åsa Duell</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>132329250</v>
       </c>
       <c r="B21" t="n">
-        <v>99125</v>
+        <v>99195</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3091,6 +3022,129 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132329253</v>
+      </c>
+      <c r="B22" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sundsvik, Sundsvik, Vrm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>418229</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6575106</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hammarö</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 24616-2022 artfynd.xlsx
+++ b/artfynd/A 24616-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103401645</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -920,6 +930,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108216914</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1036,6 +1051,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124299799</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1141,6 +1161,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114932698</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1261,6 +1286,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3044693</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1377,6 +1407,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115326284</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1493,6 +1528,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115326450</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1609,6 +1649,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120382940</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1720,6 +1765,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120383082</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1831,6 +1881,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120384522</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1947,6 +2002,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120384826</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2063,6 +2123,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124299695</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2179,6 +2244,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124299908</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2299,6 +2369,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124299992</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2415,6 +2490,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124300104</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2541,6 +2621,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128919685</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2669,6 +2754,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129922695</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2784,6 +2874,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129922697</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2899,6 +2994,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129922698</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3022,6 +3122,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132329250</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3145,8 +3250,36 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132329253</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>